--- a/nr-example/ig/StructureDefinition-fr-core-informant.xlsx
+++ b/nr-example/ig/StructureDefinition-fr-core-informant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:23:45+00:00</t>
+    <t>2025-02-05T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
